--- a/src/data/weerdata_leiden.xlsx
+++ b/src/data/weerdata_leiden.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1198"/>
+  <dimension ref="A1:G1200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27953,6 +27953,52 @@
         <v>1018.9</v>
       </c>
     </row>
+    <row r="1199" spans="1:7">
+      <c r="A1199" s="2">
+        <v>45848</v>
+      </c>
+      <c r="B1199">
+        <v>24.8</v>
+      </c>
+      <c r="C1199">
+        <v>15.6</v>
+      </c>
+      <c r="D1199">
+        <v>19</v>
+      </c>
+      <c r="E1199">
+        <v>0</v>
+      </c>
+      <c r="F1199">
+        <v>1022.6</v>
+      </c>
+      <c r="G1199">
+        <v>1018.9</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:7">
+      <c r="A1200" s="2">
+        <v>45849</v>
+      </c>
+      <c r="B1200">
+        <v>24.8</v>
+      </c>
+      <c r="C1200">
+        <v>15.6</v>
+      </c>
+      <c r="D1200">
+        <v>19</v>
+      </c>
+      <c r="E1200">
+        <v>0</v>
+      </c>
+      <c r="F1200">
+        <v>1022.6</v>
+      </c>
+      <c r="G1200">
+        <v>1018.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
